--- a/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T7604_W0029F0001T0006Z000C1N64_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.099946446281808</v>
+        <v>0.3412412975207938</v>
       </c>
       <c r="D2" t="n">
-        <v>2.391950628909872</v>
+        <v>0.3886919771978542</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
